--- a/results/andar_할인율모니터링_20260907.xlsx
+++ b/results/andar_할인율모니터링_20260907.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H177"/>
+  <dimension ref="A1:H182"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -739,12 +739,12 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.6</t>
         </is>
       </c>
     </row>
@@ -991,10 +991,14 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1197,7 +1201,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>8,043</t>
+          <t>8,047</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1251,37 +1255,37 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=9620&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=15403&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>EMTBG-12</t>
+          <t>EOTBG-21</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>데일리 쇼퍼백</t>
+          <t>데일리 라운드백</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>65,000</t>
+          <t>75,000</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>49,000</t>
+          <t>55,000</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>25%</t>
+          <t>27%</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>1,402</t>
+          <t>115</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1293,37 +1297,37 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=15403&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=9620&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>EOTBG-21</t>
+          <t>EMTBG-12</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>데일리 라운드백</t>
+          <t>데일리 쇼퍼백</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>75,000</t>
+          <t>65,000</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>55,000</t>
+          <t>49,000</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>27%</t>
+          <t>25%</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>1,402</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1335,195 +1339,195 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=13862&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=16868&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>EOTBG-03</t>
+          <t>EPTBG-03</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>데이 앤 트래블 숄더백</t>
+          <t>컴팩트 포켓 크로스백</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>79,000</t>
+          <t>65,000</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>59,000</t>
+          <t>45,000</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>25%</t>
+          <t>31%</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>122</t>
+          <t>128</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>4.9</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=16868&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=13862&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>EPTBG-03</t>
+          <t>EOTBG-03</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>컴팩트 포켓 크로스백</t>
+          <t>데이 앤 트래블 숄더백</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>65,000</t>
+          <t>79,000</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>45,000</t>
+          <t>59,000</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>31%</t>
+          <t>25%</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>128</t>
+          <t>122</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.9</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=8817&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=16629&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>EMTSC-03</t>
+          <t>EPTET-01</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>[1&amp;1] 논슬립 서포트 풀 토삭스 (HOLE)</t>
+          <t>언더웨어 파우치</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>21,800</t>
+          <t>20,000</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>17,800</t>
+          <t>20,000</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>18%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>4,816</t>
+          <t>337</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=15372&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=8817&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>EOTBG-16</t>
+          <t>EMTSC-03</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>폴더블 미니백 2.0</t>
+          <t>[1&amp;1] 논슬립 서포트 풀 토삭스 (HOLE)</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>39,000</t>
+          <t>21,800</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>29,000</t>
+          <t>17,800</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>26%</t>
+          <t>18%</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>285</t>
+          <t>4,816</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.7</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=17443&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=15372&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>EPTSC-04</t>
+          <t>EOTBG-16</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>[3 SET] 필라테스 삭스</t>
+          <t>폴더블 미니백 2.0</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>41,700</t>
+          <t>39,000</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>30,900</t>
+          <t>29,000</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1533,291 +1537,291 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>387</t>
+          <t>285</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=17443&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=10940&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>EPTSC-05</t>
+          <t>ENTBG-03</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>[3 SET] 필라테스 삭스</t>
+          <t>데일리 스트링 쇼퍼백</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>41,700</t>
+          <t>79,000</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>30,900</t>
+          <t>79,000</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>26%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>387</t>
+          <t>726</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.9</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=17443&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=13409&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>EPTSC-06</t>
+          <t>EOTBG-10</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>[3 SET] 필라테스 삭스</t>
+          <t>에어플라이 투웨이 프리런 백 3.0</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>41,700</t>
+          <t>35,000</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>30,900</t>
+          <t>32,000</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>26%</t>
+          <t>9%</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>387</t>
+          <t>1,137</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>3.0</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=10940&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=12318&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>ENTBG-03</t>
+          <t>ENTBG-13</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>데일리 스트링 쇼퍼백</t>
+          <t>데일리 스퀘어백</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>79,000</t>
+          <t>69,000</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>79,000</t>
+          <t>49,000</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>29%</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>726</t>
+          <t>429</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>4.9</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=13409&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=17443&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>EOTBG-10</t>
+          <t>EPTSC-04</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>에어플라이 투웨이 프리런 백 3.0</t>
+          <t>[3 SET] 필라테스 삭스</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>35,000</t>
+          <t>41,700</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>32,000</t>
+          <t>30,900</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>9%</t>
+          <t>26%</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>1,137</t>
+          <t>390</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>4.7</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=12318&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=17443&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>ENTBG-13</t>
+          <t>EPTSC-05</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>데일리 스퀘어백</t>
+          <t>[3 SET] 필라테스 삭스</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>69,000</t>
+          <t>41,700</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>49,000</t>
+          <t>30,900</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>29%</t>
+          <t>26%</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>429</t>
+          <t>390</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.7</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=10478&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=17443&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>ENTBG-05</t>
+          <t>EPTSC-06</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>미니 숄더 앤 크로스백</t>
+          <t>[3 SET] 필라테스 삭스</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>49,000</t>
+          <t>41,700</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>49,000</t>
+          <t>30,900</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>26%</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>5,114</t>
+          <t>390</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>4.9</t>
+          <t>4.7</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=16629&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=10478&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>EPTET-01</t>
+          <t>ENTBG-05</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>언더웨어 파우치</t>
+          <t>미니 숄더 앤 크로스백</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>20,000</t>
+          <t>49,000</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>20,000</t>
+          <t>49,000</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1827,49 +1831,49 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>337</t>
+          <t>5,117</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.9</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=13838&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=15369&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>EOTFB-01</t>
+          <t>EOTBG-19</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>에어쿨링 서스테이너블 와이드 헤드밴드</t>
+          <t>위켄드 호보백</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>13,900</t>
+          <t>79,000</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>13,900</t>
+          <t>59,000</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>25%</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>2,398</t>
+          <t>62</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -1881,37 +1885,37 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=15369&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=13838&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>EOTBG-19</t>
+          <t>EOTFB-01</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>위켄드 호보백</t>
+          <t>에어쿨링 서스테이너블 와이드 헤드밴드</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>79,000</t>
+          <t>13,900</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>59,000</t>
+          <t>13,900</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>25%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>2,407</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2217,84 +2221,84 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=15143&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=6952&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>EOTBG-17</t>
+          <t>EJFST-02</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>3 in 1 캐리온 더플백</t>
+          <t>릴렉스 요가링</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>109,000</t>
+          <t>5,900</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>85,000</t>
+          <t>5,900</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>22%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>6,583</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>4.9</t>
+          <t>4.7</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=6952&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=15143&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>EJFST-02</t>
+          <t>EOTBG-17</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>릴렉스 요가링</t>
+          <t>3 in 1 캐리온 더플백</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>5,900</t>
+          <t>109,000</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>5,900</t>
+          <t>85,000</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>22%</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>6,581</t>
+          <t>42</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.9</t>
         </is>
       </c>
     </row>
@@ -2373,7 +2377,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>2,003</t>
+          <t>2,004</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -2427,27 +2431,27 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=17425&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=15629&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>EPTSC-06</t>
+          <t>EOTBG-23</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>필라테스 크루 삭스</t>
+          <t>안다르 실버 리유저블백 M</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>13,900</t>
+          <t>6,500</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>13,900</t>
+          <t>6,500</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2457,7 +2461,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>366</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -2469,27 +2473,27 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=15629&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=16844&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>EOTBG-23</t>
+          <t>EPTET-02</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>안다르 실버 리유저블백 M</t>
+          <t>언더웨어 세탁망</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>6,500</t>
+          <t>9,900</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>6,500</t>
+          <t>9,900</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2499,7 +2503,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>366</t>
+          <t>288</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -2511,27 +2515,27 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=16844&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=13843&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>EPTET-02</t>
+          <t>EOTBG-02</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>언더웨어 세탁망</t>
+          <t>액티브 라이트 백팩</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>9,900</t>
+          <t>69,000</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>9,900</t>
+          <t>69,000</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2541,7 +2545,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>288</t>
+          <t>381</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -2595,27 +2599,27 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=13843&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=17425&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>EOTBG-02</t>
+          <t>EPTSC-06</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>액티브 라이트 백팩</t>
+          <t>필라테스 크루 삭스</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>69,000</t>
+          <t>13,900</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>69,000</t>
+          <t>13,900</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2625,7 +2629,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>381</t>
+          <t>81</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -2667,7 +2671,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>10,360</t>
+          <t>10,361</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -2679,79 +2683,79 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=11027&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=11456&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>ENTSC-08</t>
+          <t>ENTSC-13</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>[5 SET] 에어컴피 크루 삭스</t>
+          <t>[1&amp;1] 논슬립 퍼포먼스 삭스</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>85,000</t>
+          <t>23,800</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>35,000</t>
+          <t>17,800</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>59%</t>
+          <t>25%</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>811</t>
+          <t>3,021</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.7</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=13853&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=11456&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>EOTBG-12</t>
+          <t>ENTSC-14</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>프리런 벨크로 러닝 벨트</t>
+          <t>[1&amp;1] 논슬립 퍼포먼스 삭스</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>35,000</t>
+          <t>23,800</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>35,000</t>
+          <t>17,800</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>25%</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>245</t>
+          <t>3,021</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -2763,37 +2767,37 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=11456&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=13853&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>ENTSC-13</t>
+          <t>EOTBG-12</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>[1&amp;1] 논슬립 퍼포먼스 삭스</t>
+          <t>프리런 벨크로 러닝 벨트</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>23,800</t>
+          <t>35,000</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>17,800</t>
+          <t>35,000</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>25%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>3,021</t>
+          <t>245</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -2805,69 +2809,69 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=11456&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=11027&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>ENTSC-14</t>
+          <t>ENTSC-08</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>[1&amp;1] 논슬립 퍼포먼스 삭스</t>
+          <t>[5 SET] 에어컴피 크루 삭스</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>23,800</t>
+          <t>85,000</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>17,800</t>
+          <t>35,000</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>25%</t>
+          <t>59%</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>3,021</t>
+          <t>811</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=13852&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=14563&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>EOTET-03</t>
+          <t>EOTMK-01</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>라이트 러닝 베스트</t>
+          <t>UV 프로텍션 골프 마스크 (벨크로)</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>79,000</t>
+          <t>23,000</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>79,000</t>
+          <t>23,000</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2877,7 +2881,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>1,099</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -2931,27 +2935,27 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=14563&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=13852&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>EOTMK-01</t>
+          <t>EOTET-03</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>UV 프로텍션 골프 마스크 (벨크로)</t>
+          <t>라이트 러닝 베스트</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>23,000</t>
+          <t>79,000</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>23,000</t>
+          <t>79,000</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2961,7 +2965,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>1,099</t>
+          <t>99</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -3015,27 +3019,27 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=6660&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=15408&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>EKPMT-03</t>
+          <t>EOTSC-14</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>릴렉스 논슬립 요가 타월</t>
+          <t>맨즈 논슬립 풀 토삭스</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>35,900</t>
+          <t>11,900</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>35,900</t>
+          <t>11,900</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -3045,39 +3049,39 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>1,558</t>
+          <t>103</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.6</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=5145&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=10188&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>EJPFR-04</t>
+          <t>EMTRB-01</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>릴렉스 폼롤러 Ⅱ</t>
+          <t>서포트 힙 밴드</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>39,000</t>
+          <t>8,900</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>39,000</t>
+          <t>8,900</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -3087,7 +3091,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>6,362</t>
+          <t>1,369</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -3099,27 +3103,27 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=5837&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=10188&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>EJFMB-03</t>
+          <t>EMTRB-02</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>릴렉스 짐볼 65cm</t>
+          <t>서포트 힙 밴드</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>19,000</t>
+          <t>8,900</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>19,000</t>
+          <t>8,900</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -3129,12 +3133,12 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>2,110</t>
+          <t>1,369</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
@@ -3146,7 +3150,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>EMTRB-01</t>
+          <t>EMTRB-03</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -3183,27 +3187,27 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=10188&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=17423&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>EMTRB-02</t>
+          <t>EPTSC-04</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>서포트 힙 밴드</t>
+          <t>필라테스 토삭스</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>8,900</t>
+          <t>13,900</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>8,900</t>
+          <t>13,900</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -3213,7 +3217,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>1,369</t>
+          <t>98</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -3225,27 +3229,27 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=10188&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=5837&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>EMTRB-03</t>
+          <t>EJFMB-03</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>서포트 힙 밴드</t>
+          <t>릴렉스 짐볼 65cm</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>8,900</t>
+          <t>19,000</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>8,900</t>
+          <t>19,000</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -3255,39 +3259,39 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>1,369</t>
+          <t>2,110</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.7</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=17423&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=5145&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>EPTSC-04</t>
+          <t>EJPFR-04</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>필라테스 토삭스</t>
+          <t>릴렉스 폼롤러 Ⅱ</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>13,900</t>
+          <t>39,000</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>13,900</t>
+          <t>39,000</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -3297,7 +3301,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>6,362</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -3309,27 +3313,27 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=15408&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=15409&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>EOTSC-14</t>
+          <t>EOTSC-15</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>맨즈 논슬립 풀 토삭스</t>
+          <t>논슬립 퍼포먼스 풀 토삭스</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>11,900</t>
+          <t>12,900</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>11,900</t>
+          <t>12,900</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -3339,39 +3343,39 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>152</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>4.6</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=15409&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=6660&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>EOTSC-15</t>
+          <t>EKPMT-03</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>논슬립 퍼포먼스 풀 토삭스</t>
+          <t>릴렉스 논슬립 요가 타월</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>12,900</t>
+          <t>35,900</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>12,900</t>
+          <t>35,900</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -3381,7 +3385,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>152</t>
+          <t>1,558</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -3393,27 +3397,27 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=10554&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=9989&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>ENTMK-01</t>
+          <t>EMTET-02</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>UV 프로텍션 맨즈 골프 마스크</t>
+          <t>소프트 쿠셔닝 훌라후프</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>23,000</t>
+          <t>25,000</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>23,000</t>
+          <t>25,000</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -3423,12 +3427,12 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>1,535</t>
+          <t>624</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.7</t>
         </is>
       </c>
     </row>
@@ -3477,79 +3481,79 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=15385&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=13604&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>EOTSC-16</t>
+          <t>EOTSV-01</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>[1&amp;1] 논슬립 스킨 토삭스</t>
+          <t>[1&amp;1] 하이 서포트 무릎 보호대</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>25,800</t>
+          <t>29,800</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>19,900</t>
+          <t>24,900</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>23%</t>
+          <t>16%</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>514</t>
+          <t>705</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.7</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=15385&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=10554&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>EOTSC-17</t>
+          <t>ENTMK-01</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>[1&amp;1] 논슬립 스킨 토삭스</t>
+          <t>UV 프로텍션 맨즈 골프 마스크</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>25,800</t>
+          <t>23,000</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>19,900</t>
+          <t>23,000</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>23%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>514</t>
+          <t>1,535</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -3561,69 +3565,69 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=13604&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=16631&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>EOTSV-01</t>
+          <t>EPTSV-03</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>[1&amp;1] 하이 서포트 무릎 보호대</t>
+          <t>컴프레션 카프 슬리브 (종아리 보호대)</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>29,800</t>
+          <t>14,900</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>24,900</t>
+          <t>14,900</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>16%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>704</t>
+          <t>244</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=16631&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=16650&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>EPTSV-03</t>
+          <t>EPTCP-02</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>컴프레션 카프 슬리브 (종아리 보호대)</t>
+          <t>시그니처 로고 나일론 볼캡</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>14,900</t>
+          <t>39,000</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>14,900</t>
+          <t>39,000</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3633,123 +3637,123 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>243</t>
+          <t>58</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.9</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=16650&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=15385&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>EPTCP-02</t>
+          <t>EOTSC-16</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>시그니처 로고 나일론 볼캡</t>
+          <t>[1&amp;1] 논슬립 스킨 토삭스</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>39,000</t>
+          <t>25,800</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>39,000</t>
+          <t>19,900</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>23%</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>514</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>4.9</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=9989&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=15385&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>EMTET-02</t>
+          <t>EOTSC-17</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>소프트 쿠셔닝 훌라후프</t>
+          <t>[1&amp;1] 논슬립 스킨 토삭스</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>25,000</t>
+          <t>25,800</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>25,000</t>
+          <t>19,900</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>23%</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>623</t>
+          <t>514</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=13842&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=14085&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>EOTBG-04</t>
+          <t>EOTSV-04</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>데님 포켓 숄더백</t>
+          <t>프리런 라이트 러닝 밴드</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>59,000</t>
+          <t>32,000</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>59,000</t>
+          <t>32,000</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3759,39 +3763,39 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>127</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.2</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=14085&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=13842&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>EOTSV-04</t>
+          <t>EOTBG-04</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>프리런 라이트 러닝 밴드</t>
+          <t>데님 포켓 숄더백</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>32,000</t>
+          <t>59,000</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>32,000</t>
+          <t>59,000</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3801,12 +3805,12 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>127</t>
+          <t>39</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>4.2</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
@@ -3855,27 +3859,27 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=13859&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=12765&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>ENTSO-12</t>
+          <t>ENTBG-16</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>안다르 제트플라이 (맨즈)</t>
+          <t>라이트 패딩 쇼퍼백</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>139,000</t>
+          <t>69,000</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>139,000</t>
+          <t>69,000</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3885,39 +3889,39 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>695</t>
+          <t>623</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=12765&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=16033&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>ENTBG-16</t>
+          <t>EOTMK-02</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>라이트 패딩 쇼퍼백</t>
+          <t>소프텐션 넥마스크</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>69,000</t>
+          <t>32,000</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>69,000</t>
+          <t>32,000</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3927,7 +3931,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>623</t>
+          <t>157</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -3939,27 +3943,27 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=16033&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=15377&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>EOTMK-02</t>
+          <t>EOTGL-04</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>소프텐션 넥마스크</t>
+          <t>논슬립 스킨 요기 글러브</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>32,000</t>
+          <t>10,900</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>32,000</t>
+          <t>10,900</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3969,39 +3973,39 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>157</t>
+          <t>189</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.5</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=15377&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=11039&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>EOTGL-04</t>
+          <t>ENTFB-01</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>논슬립 스킨 요기 글러브</t>
+          <t>에어쿨링 라인 스크런치</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>10,900</t>
+          <t>8,900</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>10,900</t>
+          <t>8,900</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -4011,39 +4015,39 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>189</t>
+          <t>765</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=11039&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=13407&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>ENTFB-01</t>
+          <t>EOTSV-03</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>에어쿨링 라인 스크런치</t>
+          <t>서포트 허리 보호대</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>8,900</t>
+          <t>34,000</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>8,900</t>
+          <t>34,000</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -4053,81 +4057,81 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>765</t>
+          <t>179</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.7</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=8621&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=10953&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>EMTSV-06</t>
+          <t>ENTSC-07</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>에어쿨링 손목 보호대</t>
+          <t>[3 SET] 에어컴피 크루 삭스</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>15,900</t>
+          <t>51,000</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>15,900</t>
+          <t>29,000</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>43%</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>1,088</t>
+          <t>561</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.9</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=13407&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=8621&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>EOTSV-03</t>
+          <t>EMTSV-06</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>서포트 허리 보호대</t>
+          <t>에어쿨링 손목 보호대</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>34,000</t>
+          <t>15,900</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>34,000</t>
+          <t>15,900</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -4137,7 +4141,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>177</t>
+          <t>1,089</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -4149,79 +4153,79 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=10953&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=6661&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>ENTSC-07</t>
+          <t>EKPMB-01</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>[3 SET] 에어컴피 크루 삭스</t>
+          <t>릴렉스 웨이트볼 0.5kg</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>51,000</t>
+          <t>6,900</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>29,000</t>
+          <t>6,900</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>43%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>561</t>
+          <t>693</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>4.9</t>
+          <t>4.7</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=6661&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=15431&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>EKPMB-01</t>
+          <t>ENTSC-19</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>릴렉스 웨이트볼 0.5kg</t>
+          <t>[1&amp;1] 맨즈 논슬립 토삭스</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>6,900</t>
+          <t>23,800</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>6,900</t>
+          <t>16,900</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>29%</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>692</t>
+          <t>306</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -4238,7 +4242,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>ENTSC-19</t>
+          <t>EOTSC-14</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -4263,7 +4267,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>305</t>
+          <t>306</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -4275,37 +4279,37 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=15431&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=6664&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>EOTSC-14</t>
+          <t>EKPRB-04</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>[1&amp;1] 맨즈 논슬립 토삭스</t>
+          <t>릴렉스 3레벨 스트레칭 롱밴드</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>23,800</t>
+          <t>34,900</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>16,900</t>
+          <t>34,900</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>29%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>305</t>
+          <t>468</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -4347,7 +4351,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>1,325</t>
+          <t>1,326</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -4359,27 +4363,27 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=13404&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=16637&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>EOTGL-01</t>
+          <t>EPTFB-02</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>짐 글러브 2.0</t>
+          <t>퍼포먼스 심리스 손목밴드</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>25,000</t>
+          <t>6,900</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>25,000</t>
+          <t>6,900</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -4389,7 +4393,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>287</t>
+          <t>265</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -4401,27 +4405,27 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=6664&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=13806&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>EKPRB-04</t>
+          <t>EOTSC-05</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>릴렉스 3레벨 스트레칭 롱밴드</t>
+          <t>올데이 수피마 앵클 삭스</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>34,900</t>
+          <t>6,900</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>34,900</t>
+          <t>6,900</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -4431,7 +4435,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>468</t>
+          <t>474</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -4443,27 +4447,27 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=13806&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=13404&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>EOTSC-05</t>
+          <t>EOTGL-01</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>올데이 수피마 앵클 삭스</t>
+          <t>짐 글러브 2.0</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>6,900</t>
+          <t>25,000</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>6,900</t>
+          <t>25,000</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -4473,39 +4477,39 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>473</t>
+          <t>287</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=16637&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=14562&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>EPTFB-02</t>
+          <t>EOTBG-11</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>퍼포먼스 심리스 손목밴드</t>
+          <t>메쉬 파우치</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>6,900</t>
+          <t>29,000</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>6,900</t>
+          <t>29,000</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -4515,39 +4519,39 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>265</t>
+          <t>190</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.7</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=14562&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=11458&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>EOTBG-11</t>
+          <t>ENTSC-13</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>메쉬 파우치</t>
+          <t>논슬립 퍼포먼스 크루삭스</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>29,000</t>
+          <t>11,900</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>29,000</t>
+          <t>11,900</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -4557,7 +4561,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>190</t>
+          <t>666</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -4569,27 +4573,27 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=11458&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=13410&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>ENTSC-13</t>
+          <t>EOTSC-09</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>논슬립 퍼포먼스 크루삭스</t>
+          <t>컴프레션 러닝 니삭스</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>11,900</t>
+          <t>14,900</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>11,900</t>
+          <t>14,900</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -4599,91 +4603,91 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>666</t>
+          <t>345</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.9</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=13410&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=6828&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>EOTSC-09</t>
+          <t>EKPET-01</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>컴프레션 러닝 니삭스</t>
+          <t>[1&amp;1] 릴렉스 소프트 웨이트바 1kg</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>14,900</t>
+          <t>41,800</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>14,900</t>
+          <t>35,600</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>15%</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>345</t>
+          <t>594</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>4.9</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=6828&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=13851&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>EKPET-01</t>
+          <t>EOTCP-03</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>[1&amp;1] 릴렉스 소프트 웨이트바 1kg</t>
+          <t>쿨 라운드 볼캡</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>41,800</t>
+          <t>45,000</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>35,600</t>
+          <t>45,000</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>594</t>
+          <t>100</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -4737,27 +4741,27 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=13851&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=16847&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>EOTCP-03</t>
+          <t>EPTSC-02</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>쿨 라운드 볼캡</t>
+          <t>하이 쿠션 테이핑 러닝 삭스</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>45,000</t>
+          <t>12,900</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>45,000</t>
+          <t>12,900</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4767,12 +4771,12 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>91</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.7</t>
         </is>
       </c>
     </row>
@@ -4863,27 +4867,27 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=16847&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=13805&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>EPTSC-02</t>
+          <t>EOTSC-04</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>하이 쿠션 테이핑 러닝 삭스</t>
+          <t>올데이 수피마 스니커즈 삭스</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>12,900</t>
+          <t>5,900</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>12,900</t>
+          <t>5,900</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4893,49 +4897,49 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>429</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=11130&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=13405&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>ENTSV-01</t>
+          <t>EOTSV-01</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>[1&amp;1] 3D 쿨링 팔토시</t>
+          <t>하이 서포트 무릎 보호대</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>29,800</t>
+          <t>14,900</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>25,900</t>
+          <t>14,900</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>13%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>705</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -4989,42 +4993,42 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=13805&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=11130&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>EOTSC-04</t>
+          <t>ENTSV-01</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>올데이 수피마 스니커즈 삭스</t>
+          <t>[1&amp;1] 3D 쿨링 팔토시</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>5,900</t>
+          <t>29,800</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>5,900</t>
+          <t>25,900</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>13%</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>428</t>
+          <t>550</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.7</t>
         </is>
       </c>
     </row>
@@ -5157,27 +5161,27 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=17437&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=13859&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>EPTCP-03</t>
+          <t>ENTSO-12</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>썬가드 와이드 버킷햇</t>
+          <t>안다르 제트플라이 (맨즈)</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>69,000</t>
+          <t>139,000</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>69,000</t>
+          <t>139,000</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -5187,138 +5191,138 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>695</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>4.6</t>
+          <t>4.7</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=10657&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=17437&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>EMTSC-17</t>
+          <t>EPTCP-03</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>[3 SET] 맨즈 클래식 삭스</t>
+          <t>썬가드 와이드 버킷햇</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>20,700</t>
+          <t>69,000</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>17,900</t>
+          <t>69,000</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>14%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>223</t>
+          <t>62</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.6</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=8836&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=10657&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>EMTSV-01</t>
+          <t>EMTSC-17</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>[1&amp;1] 서포트 팔꿈치 보호대</t>
+          <t>[3 SET] 맨즈 클래식 삭스</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>27,800</t>
+          <t>20,700</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>22,900</t>
+          <t>17,900</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>18%</t>
+          <t>14%</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>589</t>
+          <t>223</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=15375&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=8836&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>EOTSC-16</t>
+          <t>EMTSV-01</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>논슬립 스킨 하프 토삭스</t>
+          <t>[1&amp;1] 서포트 팔꿈치 보호대</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>12,900</t>
+          <t>27,800</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>12,900</t>
+          <t>22,900</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>18%</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>108</t>
+          <t>590</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>4.9</t>
+          <t>4.7</t>
         </is>
       </c>
     </row>
@@ -5367,27 +5371,27 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=8728&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=15375&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>EMTSC-05</t>
+          <t>EOTSC-16</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>논슬립 서포트 하프 토삭스 (SOLID)</t>
+          <t>논슬립 스킨 하프 토삭스</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>9,900</t>
+          <t>12,900</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>9,900</t>
+          <t>12,900</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -5397,39 +5401,39 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>561</t>
+          <t>108</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.9</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=14561&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=11457&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>EOTBG-05</t>
+          <t>ENTSC-12</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>메쉬 포켓 비치백</t>
+          <t>논슬립 퍼포먼스 토삭스</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>49,000</t>
+          <t>12,900</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>49,000</t>
+          <t>12,900</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -5439,49 +5443,49 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>4,135</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.7</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=17857&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=8728&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>EPTSC-03</t>
+          <t>EMTSC-05</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>[1&amp;1] 데일리 루즈 삭스</t>
+          <t>논슬립 서포트 하프 토삭스 (SOLID)</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>23,800</t>
+          <t>9,900</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>18,900</t>
+          <t>9,900</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>21%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>561</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -5493,37 +5497,37 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=13605&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=14561&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>EOTSV-02</t>
+          <t>EOTBG-05</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>[1&amp;1] 하이 서포트 팔꿈치 보호대</t>
+          <t>메쉬 포켓 비치백</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>29,800</t>
+          <t>49,000</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>24,900</t>
+          <t>49,000</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>16%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>154</t>
+          <t>57</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -5535,79 +5539,79 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=13405&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=17857&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>EOTSV-01</t>
+          <t>EPTSC-03</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>하이 서포트 무릎 보호대</t>
+          <t>[1&amp;1] 데일리 루즈 삭스</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>14,900</t>
+          <t>23,800</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>14,900</t>
+          <t>18,900</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>21%</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>704</t>
+          <t>28</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=15867&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=13605&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>EOTSC-18</t>
+          <t>EOTSV-02</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>[1&amp;1] 올데이 기모 삭스</t>
+          <t>[1&amp;1] 하이 서포트 팔꿈치 보호대</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>21,800</t>
+          <t>29,800</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>15,900</t>
+          <t>24,900</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>27%</t>
+          <t>16%</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>225</t>
+          <t>154</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -5619,69 +5623,69 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=11457&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=15867&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>ENTSC-12</t>
+          <t>EOTSC-18</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>논슬립 퍼포먼스 토삭스</t>
+          <t>[1&amp;1] 올데이 기모 삭스</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>12,900</t>
+          <t>21,800</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>12,900</t>
+          <t>15,900</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>27%</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>4,135</t>
+          <t>225</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=8769&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=12778&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>EMTSV-02</t>
+          <t>ENTBG-14</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>서포트 발목 보호대</t>
+          <t>웨이브 패딩 파우치</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>13,900</t>
+          <t>32,000</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>13,900</t>
+          <t>32,000</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -5691,39 +5695,39 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>716</t>
+          <t>192</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=12778&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=6665&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>ENTBG-14</t>
+          <t>EKPRB-05</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>웨이브 패딩 파우치</t>
+          <t>릴렉스 4레벨 힙 밴드</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>32,000</t>
+          <t>21,900</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>32,000</t>
+          <t>21,900</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -5733,7 +5737,7 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>192</t>
+          <t>527</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -5745,69 +5749,69 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=6665&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=9612&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>EKPRB-05</t>
+          <t>EMTSC-28</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>릴렉스 4레벨 힙 밴드</t>
+          <t>[1&amp;1] 리브드 셔링 루즈 삭스</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>21,900</t>
+          <t>21,800</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>21,900</t>
+          <t>17,900</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>18%</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>527</t>
+          <t>395</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.7</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=11459&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=13566&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>ENTSC-14</t>
+          <t>EOTSC-10</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>논슬립 퍼포먼스 니삭스</t>
+          <t>시그니처 로고 맨즈 크루 삭스</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>13,900</t>
+          <t>7,900</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>13,900</t>
+          <t>7,900</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -5817,7 +5821,7 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>752</t>
+          <t>214</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
@@ -5829,69 +5833,69 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=9612&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=15732&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>EMTSC-28</t>
+          <t>EOTSC-11</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>[1&amp;1] 리브드 셔링 루즈 삭스</t>
+          <t>웜 레그 롱 워머</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>21,800</t>
+          <t>25,000</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>17,900</t>
+          <t>25,000</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>18%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>395</t>
+          <t>113</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=13566&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=17440&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>EOTSC-10</t>
+          <t>EPTET-03</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>시그니처 로고 맨즈 크루 삭스</t>
+          <t>안다르 3단 양우산</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>7,900</t>
+          <t>29,000</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>7,900</t>
+          <t>29,000</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -5901,39 +5905,39 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>213</t>
+          <t>35</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.4</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=15732&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=8769&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>EOTSC-11</t>
+          <t>EMTSV-02</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>웜 레그 롱 워머</t>
+          <t>서포트 발목 보호대</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>25,000</t>
+          <t>13,900</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>25,000</t>
+          <t>13,900</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -5943,81 +5947,81 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>113</t>
+          <t>716</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.7</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=17440&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=10191&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>EPTET-03</t>
+          <t>EMTSC-26</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>안다르 3단 양우산</t>
+          <t>[1&amp;1] 램스울 크루 삭스</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>29,000</t>
+          <t>19,800</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>29,000</t>
+          <t>17,900</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>10%</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>840</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>4.4</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=16031&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=11459&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>EOTGL-02</t>
+          <t>ENTSC-14</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>히트 런 글러브</t>
+          <t>논슬립 퍼포먼스 니삭스</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>29,000</t>
+          <t>13,900</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>29,000</t>
+          <t>13,900</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -6027,39 +6031,39 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>212</t>
+          <t>752</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=15376&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=9996&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>EOTSC-17</t>
+          <t>EMTSC-27</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>논슬립 스킨 토삭스</t>
+          <t>올라운드 오버 니삭스</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>12,900</t>
+          <t>13,900</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>12,900</t>
+          <t>13,900</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -6069,7 +6073,7 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>296</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
@@ -6081,37 +6085,37 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=10191&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=8727&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>EMTSC-26</t>
+          <t>EMTSC-04</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>[1&amp;1] 램스울 크루 삭스</t>
+          <t>논슬립 서포트 하프 토삭스 (HOLE)</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>19,800</t>
+          <t>10,900</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>17,900</t>
+          <t>10,900</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>840</t>
+          <t>643</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
@@ -6123,27 +6127,27 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=8727&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=13406&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>EMTSC-04</t>
+          <t>EOTSV-02</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>논슬립 서포트 하프 토삭스 (HOLE)</t>
+          <t>하이 서포트 팔꿈치 보호대</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>10,900</t>
+          <t>14,900</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>10,900</t>
+          <t>14,900</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
@@ -6153,7 +6157,7 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>643</t>
+          <t>154</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -6165,27 +6169,27 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=9996&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=15376&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>EMTSC-27</t>
+          <t>EOTSC-17</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>올라운드 오버 니삭스</t>
+          <t>논슬립 스킨 토삭스</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>13,900</t>
+          <t>12,900</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>13,900</t>
+          <t>12,900</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
@@ -6195,7 +6199,7 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>295</t>
+          <t>86</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -6207,27 +6211,27 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=13406&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=12793&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>EOTSV-02</t>
+          <t>ENTMU-01</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>하이 서포트 팔꿈치 보호대</t>
+          <t>소프트 니트 머플러</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>14,900</t>
+          <t>19,900</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>14,900</t>
+          <t>19,900</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
@@ -6237,7 +6241,7 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>154</t>
+          <t>472</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
@@ -6249,27 +6253,27 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=12793&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=8770&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>ENTMU-01</t>
+          <t>EMTSV-03</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>소프트 니트 머플러</t>
+          <t>서포트 무릎 보호대</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>19,900</t>
+          <t>13,900</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>19,900</t>
+          <t>13,900</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
@@ -6279,39 +6283,39 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>472</t>
+          <t>2,004</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.5</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=15144&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=11061&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>EOTBO-01</t>
+          <t>ENTSV-01</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>액티브 스포츠 보틀 (650ml)</t>
+          <t>3D 쿨링 팔토시</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>49,000</t>
+          <t>14,900</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>49,000</t>
+          <t>14,900</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
@@ -6321,39 +6325,39 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>254</t>
+          <t>550</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.7</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=8770&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=8726&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>EMTSV-03</t>
+          <t>EMTSC-03</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>서포트 무릎 보호대</t>
+          <t>논슬립 서포트 풀 토삭스 (HOLE)</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>13,900</t>
+          <t>10,900</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>13,900</t>
+          <t>10,900</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
@@ -6363,12 +6367,12 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>2,003</t>
+          <t>4,816</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>4.7</t>
         </is>
       </c>
     </row>
@@ -6405,7 +6409,7 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>93</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
@@ -6459,27 +6463,27 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=17436&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=17415&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>EPTSV-01</t>
+          <t>EPTSC-01</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>3D 쿨링 핑거홀 팔토시</t>
+          <t>쿨 메쉬 서포트 러닝 삭스</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>15,900</t>
+          <t>10,900</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>15,900</t>
+          <t>10,900</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
@@ -6489,7 +6493,7 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>178</t>
+          <t>115</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
@@ -6531,7 +6535,7 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>237</t>
+          <t>238</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
@@ -6585,27 +6589,27 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=11061&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=16031&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>ENTSV-01</t>
+          <t>EOTGL-02</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>3D 쿨링 팔토시</t>
+          <t>히트 런 글러브</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>14,900</t>
+          <t>29,000</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>14,900</t>
+          <t>29,000</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
@@ -6615,7 +6619,7 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>212</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
@@ -6669,27 +6673,27 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=17415&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=17386&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>EPTSC-01</t>
+          <t>EPTSC-07</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>쿨 메쉬 서포트 러닝 삭스</t>
+          <t>맨즈 필라테스 앵클 삭스</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>10,900</t>
+          <t>13,900</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>10,900</t>
+          <t>13,900</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
@@ -6699,39 +6703,39 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>5.0</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=16036&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=15151&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>EOTCP-06</t>
+          <t>EOTBG-22</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>소프트 니트 버킷햇</t>
+          <t>투포켓 로고 캔버스백</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>45,000</t>
+          <t>49,000</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>45,000</t>
+          <t>49,000</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
@@ -6741,39 +6745,39 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>35</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.7</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=11725&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=15144&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>ENTFB-04</t>
+          <t>EOTBO-01</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>더블 링글 손목밴드</t>
+          <t>액티브 스포츠 보틀 (650ml)</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>4,900</t>
+          <t>49,000</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>4,900</t>
+          <t>49,000</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
@@ -6783,39 +6787,39 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>433</t>
+          <t>255</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>4.9</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=6666&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=16036&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>EKPET-01</t>
+          <t>EOTCP-06</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>릴렉스 소프트 웨이트바 1kg</t>
+          <t>소프트 니트 버킷햇</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>20,900</t>
+          <t>45,000</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>20,900</t>
+          <t>45,000</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
@@ -6825,7 +6829,7 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>594</t>
+          <t>52</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
@@ -6837,27 +6841,27 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=8768&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=11725&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>EMTSV-01</t>
+          <t>ENTFB-04</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>서포트 팔꿈치 보호대</t>
+          <t>더블 링글 손목밴드</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>13,900</t>
+          <t>4,900</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>13,900</t>
+          <t>4,900</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
@@ -6867,39 +6871,39 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>589</t>
+          <t>434</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.9</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=12795&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=6666&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>ENTCP-05</t>
+          <t>EKPET-01</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>소프트 니트 비니</t>
+          <t>릴렉스 소프트 웨이트바 1kg</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>19,900</t>
+          <t>20,900</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>19,900</t>
+          <t>20,900</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
@@ -6909,39 +6913,39 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>361</t>
+          <t>594</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=16640&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=8768&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>EPTBG-05</t>
+          <t>EMTSV-01</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>안다르 시그니처 로고 에코백</t>
+          <t>서포트 팔꿈치 보호대</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>39,000</t>
+          <t>13,900</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>39,000</t>
+          <t>13,900</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
@@ -6951,39 +6955,39 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>590</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>4.2</t>
+          <t>4.7</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=12783&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=12795&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>ENTSC-26</t>
+          <t>ENTCP-05</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>니트 기모 오버 니삭스</t>
+          <t>소프트 니트 비니</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>17,900</t>
+          <t>19,900</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>17,900</t>
+          <t>19,900</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
@@ -6993,39 +6997,39 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>354</t>
+          <t>361</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.7</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=17386&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=16640&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>EPTSC-07</t>
+          <t>EPTBG-05</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>맨즈 필라테스 앵클 삭스</t>
+          <t>안다르 시그니처 로고 에코백</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>13,900</t>
+          <t>39,000</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>13,900</t>
+          <t>39,000</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
@@ -7035,91 +7039,91 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>4.2</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=10939&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=12783&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>ENTSC-07</t>
+          <t>ENTSC-26</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>에어컴피 크루 삭스</t>
+          <t>니트 기모 오버 니삭스</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>17,000</t>
+          <t>17,900</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>12,000</t>
+          <t>17,900</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>29%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>561</t>
+          <t>354</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>4.9</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=16034&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=17446&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>EOTGL-03</t>
+          <t>EPTSV-01</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>소프트 니트 플립 글러브</t>
+          <t>[1&amp;1] 3D 쿨링 핑거홀 팔토시</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>23,900</t>
+          <t>31,800</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>23,900</t>
+          <t>26,900</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>15%</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>178</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
@@ -7131,69 +7135,69 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=12792&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=10939&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>ENTGL-05</t>
+          <t>ENTSC-07</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>니트 글러브</t>
+          <t>에어컴피 크루 삭스</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>23,900</t>
+          <t>17,000</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>23,900</t>
+          <t>12,000</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>29%</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>371</t>
+          <t>561</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.9</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=17842&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=16034&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>EPTSC-03</t>
+          <t>EOTGL-03</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>데일리 루즈 삭스</t>
+          <t>소프트 니트 플립 글러브</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>11,900</t>
+          <t>23,900</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>11,900</t>
+          <t>23,900</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
@@ -7203,91 +7207,91 @@
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>83</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.7</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=15719&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=12792&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>EOTSC-19</t>
+          <t>ENTGL-05</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>[1&amp;1] 레그 워머</t>
+          <t>니트 글러브</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>21,800</t>
+          <t>23,900</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>15,900</t>
+          <t>23,900</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>27%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>230</t>
+          <t>371</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.7</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=15719&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=17842&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>EOTSC-20</t>
+          <t>EPTSC-03</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>[1&amp;1] 레그 워머</t>
+          <t>데일리 루즈 삭스</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>21,800</t>
+          <t>11,900</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>15,900</t>
+          <t>11,900</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>27%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>230</t>
+          <t>28</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
@@ -7299,111 +7303,111 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=9599&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=15719&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>EMTSC-28</t>
+          <t>EOTSC-19</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>리브드 셔링 루즈 삭스</t>
+          <t>[1&amp;1] 레그 워머</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>10,900</t>
+          <t>21,800</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>10,900</t>
+          <t>15,900</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>27%</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>395</t>
+          <t>230</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=16035&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=15719&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>EOTSC-12</t>
+          <t>EOTSC-20</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>소프트 니트 기모 니삭스</t>
+          <t>[1&amp;1] 레그 워머</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
+          <t>21,800</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
           <t>15,900</t>
         </is>
       </c>
-      <c r="E166" t="inlineStr">
-        <is>
-          <t>15,900</t>
-        </is>
-      </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>27%</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>230</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=12794&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=9599&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>ENTFB-05</t>
+          <t>EMTSC-28</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>소프트 니트 헤드밴드</t>
+          <t>리브드 셔링 루즈 삭스</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>15,900</t>
+          <t>10,900</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>15,900</t>
+          <t>10,900</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
@@ -7413,39 +7417,39 @@
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>913</t>
+          <t>395</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.7</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=15734&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=16035&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>EOTSC-20</t>
+          <t>EOTSC-12</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>레그 미들 워머</t>
+          <t>소프트 니트 기모 니삭스</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>12,900</t>
+          <t>15,900</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>12,900</t>
+          <t>15,900</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
@@ -7455,39 +7459,39 @@
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>102</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>4.9</t>
+          <t>5.0</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=15865&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=12794&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>EOTSC-18</t>
+          <t>ENTFB-05</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>올데이 기모 삭스</t>
+          <t>소프트 니트 헤드밴드</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>10,900</t>
+          <t>15,900</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>10,900</t>
+          <t>15,900</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
@@ -7497,7 +7501,7 @@
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>225</t>
+          <t>913</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
@@ -7509,27 +7513,27 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=9993&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=15734&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>EMTSC-29</t>
+          <t>EOTSC-20</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>니트 루즈 삭스</t>
+          <t>레그 미들 워머</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>9,900</t>
+          <t>12,900</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>9,900</t>
+          <t>12,900</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
@@ -7539,39 +7543,39 @@
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>513</t>
+          <t>36</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.9</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=9988&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=15865&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>EMTSC-26</t>
+          <t>EOTSC-18</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>램스울 크루 삭스</t>
+          <t>올데이 기모 삭스</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>9,900</t>
+          <t>10,900</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>9,900</t>
+          <t>10,900</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
@@ -7581,7 +7585,7 @@
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>332</t>
+          <t>225</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
@@ -7593,17 +7597,17 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=8579&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=9993&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>EMTSC-02</t>
+          <t>EMTSC-29</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>링글 니삭스</t>
+          <t>니트 루즈 삭스</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -7623,7 +7627,7 @@
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>1,700</t>
+          <t>513</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
@@ -7635,27 +7639,27 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=16045&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=9988&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>EOTMU-01</t>
+          <t>EMTSC-26</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>스트링 패딩 넥워머</t>
+          <t>램스울 크루 삭스</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>49,000</t>
+          <t>9,900</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>49,000</t>
+          <t>9,900</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
@@ -7665,39 +7669,39 @@
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>332</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=16032&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=8579&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>EOTCP-05</t>
+          <t>EMTSC-02</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>히트 런 이어플랩 캡</t>
+          <t>링글 니삭스</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>55,000</t>
+          <t>9,900</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>55,000</t>
+          <t>9,900</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
@@ -7707,7 +7711,7 @@
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>1,700</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
@@ -7719,69 +7723,69 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=15733&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=16632&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>EOTSC-19</t>
+          <t>EPTSV-02</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>레그 숏 워머</t>
+          <t>[1&amp;1] 하이 서포트 발목 보호대</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>10,900</t>
+          <t>29,800</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>10,900</t>
+          <t>24,900</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>16%</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>110</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.7</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=13831&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=16630&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>EOTCP-02</t>
+          <t>EPTSV-02</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>데님 로고 볼캡</t>
+          <t>하이 서포트 발목 보호대</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>39,000</t>
+          <t>14,900</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>39,000</t>
+          <t>14,900</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
@@ -7791,52 +7795,262 @@
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>110</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.7</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
+          <t>https://andar.co.kr/product/detail.html?product_no=16045&amp;cate_no=2100&amp;display_group=1</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>EOTMU-01</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>스트링 패딩 넥워머</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>49,000</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>49,000</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>4.7</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>https://andar.co.kr/product/detail.html?product_no=16032&amp;cate_no=2100&amp;display_group=1</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>EOTCP-05</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>히트 런 이어플랩 캡</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>55,000</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>55,000</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>92</t>
+        </is>
+      </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>4.8</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>https://andar.co.kr/product/detail.html?product_no=15733&amp;cate_no=2100&amp;display_group=1</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>EOTSC-19</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>레그 숏 워머</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>10,900</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>10,900</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="H179" t="inlineStr">
+        <is>
+          <t>4.8</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>https://andar.co.kr/product/detail.html?product_no=13831&amp;cate_no=2100&amp;display_group=1</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>EOTCP-02</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>데님 로고 볼캡</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>39,000</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>39,000</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>4.8</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>https://andar.co.kr/product/detail.html?product_no=11110&amp;cate_no=2100&amp;display_group=1</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>ENTCP-01</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>와이드 셰이드 버킷햇</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>59,000</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>59,000</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>685</t>
+        </is>
+      </c>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>4.7</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
           <t>https://andar.co.kr/product/detail.html?product_no=11092&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
-      <c r="B177" t="inlineStr">
+      <c r="B182" t="inlineStr">
         <is>
           <t>ENTSC-05</t>
         </is>
       </c>
-      <c r="C177" t="inlineStr">
+      <c r="C182" t="inlineStr">
         <is>
           <t>에어프레시 크루 삭스</t>
         </is>
       </c>
-      <c r="D177" t="inlineStr">
+      <c r="D182" t="inlineStr">
         <is>
           <t>17,000</t>
         </is>
       </c>
-      <c r="E177" t="inlineStr">
+      <c r="E182" t="inlineStr">
         <is>
           <t>17,000</t>
         </is>
       </c>
-      <c r="F177" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="G177" t="inlineStr">
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="G182" t="inlineStr">
         <is>
           <t>575</t>
         </is>
       </c>
-      <c r="H177" t="inlineStr">
+      <c r="H182" t="inlineStr">
         <is>
           <t>4.8</t>
         </is>
